--- a/public/StructureDefinition-pghd-heartbeat.xlsx
+++ b/public/StructureDefinition-pghd-heartbeat.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:28:41-06:00</t>
+    <t>2026-09-10T16:32:51-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-heartbeat.xlsx
+++ b/public/StructureDefinition-pghd-heartbeat.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T16:07:18-05:00</t>
+    <t>2026-10-08T19:53:09-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -978,6 +978,9 @@
   </si>
   <si>
     <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/CodeSystem/observation-pghd-codes</t>
   </si>
   <si>
     <t>Observation.code.coding:PGHDCode.version</t>
@@ -1808,9 +1811,6 @@
   </si>
   <si>
     <t>Observation.component.code.coding.system</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/uv/phr/CodeSystem/observation-pghd-codes</t>
   </si>
   <si>
     <t>Observation.component:heartbeat.code.coding.version</t>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>92</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6600,10 +6600,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6720,10 +6720,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -6840,10 +6840,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6960,10 +6960,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7082,13 +7082,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>301</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>82</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>306</v>
@@ -7324,7 +7324,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>308</v>
@@ -7444,7 +7444,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>310</v>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7566,10 +7566,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7686,10 +7686,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7806,10 +7806,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7926,10 +7926,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8048,10 +8048,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8170,10 +8170,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8196,19 +8196,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8257,7 +8257,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8272,19 +8272,19 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8292,10 +8292,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8318,16 +8318,16 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8377,7 +8377,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8401,10 +8401,10 @@
         <v>295</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8412,14 +8412,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8438,19 +8438,19 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8499,7 +8499,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8514,19 +8514,19 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8534,14 +8534,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8560,19 +8560,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8621,7 +8621,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8636,19 +8636,19 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8656,10 +8656,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8682,16 +8682,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8741,7 +8741,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8762,13 +8762,13 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8776,10 +8776,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8802,17 +8802,17 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8861,7 +8861,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8876,19 +8876,19 @@
         <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8896,10 +8896,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8922,19 +8922,19 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8983,7 +8983,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8992,7 +8992,7 @@
         <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -9001,27 +9001,27 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9047,16 +9047,16 @@
         <v>190</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9081,13 +9081,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9105,7 +9105,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9114,7 +9114,7 @@
         <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>104</v>
@@ -9129,7 +9129,7 @@
         <v>135</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9140,14 +9140,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9169,16 +9169,16 @@
         <v>190</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9203,13 +9203,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9227,7 +9227,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9245,27 +9245,27 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9288,19 +9288,19 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9349,7 +9349,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9370,10 +9370,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9384,10 +9384,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9413,13 +9413,13 @@
         <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9448,10 +9448,10 @@
         <v>290</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9469,7 +9469,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9487,27 +9487,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9533,16 +9533,16 @@
         <v>190</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9570,10 +9570,10 @@
         <v>290</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9591,7 +9591,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9612,10 +9612,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9652,16 +9652,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9711,7 +9711,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9729,27 +9729,27 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9772,16 +9772,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9831,7 +9831,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9849,27 +9849,27 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9892,19 +9892,19 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9953,7 +9953,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9965,7 +9965,7 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -9974,10 +9974,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9988,10 +9988,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10106,10 +10106,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10226,14 +10226,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10255,10 +10255,10 @@
         <v>138</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>141</v>
@@ -10313,7 +10313,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10348,10 +10348,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10374,13 +10374,13 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10431,7 +10431,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10440,7 +10440,7 @@
         <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10452,10 +10452,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10466,10 +10466,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10492,13 +10492,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10549,7 +10549,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10558,7 +10558,7 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10570,10 +10570,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10584,10 +10584,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10613,16 +10613,16 @@
         <v>190</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10650,10 +10650,10 @@
         <v>116</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10671,7 +10671,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10689,13 +10689,13 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10706,10 +10706,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10735,16 +10735,16 @@
         <v>190</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10772,10 +10772,10 @@
         <v>290</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10793,7 +10793,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10811,13 +10811,13 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10828,10 +10828,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10854,17 +10854,17 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10913,7 +10913,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10937,7 +10937,7 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10948,10 +10948,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10977,10 +10977,10 @@
         <v>205</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11031,7 +11031,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11052,10 +11052,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11066,10 +11066,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11092,16 +11092,16 @@
         <v>93</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11151,7 +11151,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11172,10 +11172,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11186,10 +11186,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11212,16 +11212,16 @@
         <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11271,7 +11271,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11292,10 +11292,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11306,10 +11306,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11332,19 +11332,19 @@
         <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11381,7 +11381,7 @@
         <v>82</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
@@ -11391,7 +11391,7 @@
         <v>198</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11412,10 +11412,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11426,10 +11426,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11544,10 +11544,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11664,14 +11664,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11693,10 +11693,10 @@
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>141</v>
@@ -11751,7 +11751,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11786,10 +11786,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11815,13 +11815,13 @@
         <v>190</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O79" t="s" s="2">
         <v>289</v>
@@ -11873,7 +11873,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>92</v>
@@ -11891,7 +11891,7 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>295</v>
@@ -11908,10 +11908,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11934,19 +11934,19 @@
         <v>93</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11995,7 +11995,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12013,27 +12013,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12059,16 +12059,16 @@
         <v>190</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12093,13 +12093,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12117,7 +12117,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12126,7 +12126,7 @@
         <v>92</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>104</v>
@@ -12141,7 +12141,7 @@
         <v>135</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12152,14 +12152,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12181,16 +12181,16 @@
         <v>190</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12215,13 +12215,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12239,7 +12239,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12257,27 +12257,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12303,16 +12303,16 @@
         <v>83</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12361,7 +12361,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12382,10 +12382,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12396,13 +12396,13 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>82</v>
@@ -12424,19 +12424,19 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12485,7 +12485,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12506,10 +12506,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12520,10 +12520,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12638,10 +12638,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12758,14 +12758,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12787,10 +12787,10 @@
         <v>138</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>141</v>
@@ -12845,7 +12845,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12880,10 +12880,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12909,13 +12909,13 @@
         <v>190</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>289</v>
@@ -12967,7 +12967,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>92</v>
@@ -12985,7 +12985,7 @@
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>295</v>
@@ -13002,10 +13002,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13120,10 +13120,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13240,10 +13240,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13362,10 +13362,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13480,10 +13480,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13600,10 +13600,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13648,7 +13648,7 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>576</v>
+        <v>311</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>82</v>
@@ -13885,7 +13885,7 @@
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>82</v>
@@ -14329,7 +14329,7 @@
         <v>587</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14355,16 +14355,16 @@
         <v>588</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14413,7 +14413,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14431,19 +14431,19 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="101" hidden="true">
@@ -15295,7 +15295,7 @@
         <v>640</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15321,16 +15321,16 @@
         <v>190</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15355,13 +15355,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15379,7 +15379,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15388,7 +15388,7 @@
         <v>92</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>104</v>
@@ -15403,7 +15403,7 @@
         <v>135</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15417,11 +15417,11 @@
         <v>641</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -15443,16 +15443,16 @@
         <v>190</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15477,13 +15477,13 @@
         <v>82</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15501,7 +15501,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15519,19 +15519,19 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="110" hidden="true">
@@ -15539,7 +15539,7 @@
         <v>642</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15565,16 +15565,16 @@
         <v>83</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15623,7 +15623,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15644,10 +15644,10 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
